--- a/Unmatched_Favini_Colours.xlsx
+++ b/Unmatched_Favini_Colours.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,8 +38,14 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <color rgb="00006100"/>
+    </font>
+    <font>
+      <color rgb="009C0006"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -86,6 +92,18 @@
         <fgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -99,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -126,6 +144,19 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -505,7 +536,7 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2">
@@ -515,7 +546,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
@@ -535,7 +566,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -545,7 +576,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -574,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1260,56 +1291,56 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>Prisma</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>White</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
         <is>
           <t>favini.com/gs/en/products/prisma/</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t>Favini shows "03 White" — numbered code, not exact string</t>
-        </is>
-      </c>
-      <c r="E26" s="11" t="inlineStr">
-        <is>
-          <t>NEEDS YOUR CALL</t>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>Exact match (via 03 White Digital)</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>Real photo applied</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>Prisma</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>Ivory</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>favini.com/gs/en/products/prisma/</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr">
-        <is>
-          <t>Favini shows "05 Ivory" — numbered code, not exact string</t>
-        </is>
-      </c>
-      <c r="E27" s="11" t="inlineStr">
-        <is>
-          <t>NEEDS YOUR CALL</t>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>Exact match</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>Real photo applied</t>
         </is>
       </c>
     </row>
@@ -1368,110 +1399,110 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>Bianco Flash</t>
         </is>
       </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>Master White</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="C30" s="12" t="inlineStr">
         <is>
           <t>favini.com/gs/en/products/biancoflash/</t>
         </is>
       </c>
-      <c r="D30" s="10" t="inlineStr">
-        <is>
-          <t>No exact match (Favini: "Master")</t>
-        </is>
-      </c>
-      <c r="E30" s="10" t="inlineStr">
-        <is>
-          <t>No image at all</t>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>Mapped (confirmed same product)</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>Real photo applied (via Master)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>Bianco Flash</t>
         </is>
       </c>
-      <c r="B31" s="10" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>Bianco</t>
         </is>
       </c>
-      <c r="C31" s="10" t="inlineStr">
+      <c r="C31" s="12" t="inlineStr">
         <is>
           <t>favini.com/gs/en/products/biancoflash/</t>
         </is>
       </c>
-      <c r="D31" s="10" t="inlineStr">
-        <is>
-          <t>No exact match (Favini: "Premium")</t>
-        </is>
-      </c>
-      <c r="E31" s="10" t="inlineStr">
-        <is>
-          <t>No image at all</t>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>Mapped to Favini: Premium (confirmed)</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>Real photo applied (via Premium Digital)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="inlineStr">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>Bianco Flash</t>
         </is>
       </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>Natural White</t>
         </is>
       </c>
-      <c r="C32" s="10" t="inlineStr">
+      <c r="C32" s="12" t="inlineStr">
         <is>
           <t>favini.com/gs/en/products/biancoflash/</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr">
-        <is>
-          <t>No exact match (Favini: "Natural")</t>
-        </is>
-      </c>
-      <c r="E32" s="10" t="inlineStr">
-        <is>
-          <t>No image at all</t>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>Mapped to Favini: Natural (confirmed)</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>Real photo applied (via Natural Digital)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>Contact Natural</t>
         </is>
       </c>
-      <c r="B33" s="10" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>Natural White</t>
         </is>
       </c>
-      <c r="C33" s="10" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr">
         <is>
           <t>— (doesn't exist)</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr">
-        <is>
-          <t>Product does not exist on favini.com at all</t>
-        </is>
-      </c>
-      <c r="E33" s="10" t="inlineStr">
-        <is>
-          <t>No image at all</t>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>No dedicated Favini page — reusing Contact Pack Ivory per instruction</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>Real photo applied (borrowed from Contact Pack)</t>
         </is>
       </c>
     </row>
@@ -1638,29 +1669,29 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="A40" s="12" t="inlineStr">
         <is>
           <t>Majestic</t>
         </is>
       </c>
-      <c r="B40" s="10" t="inlineStr">
+      <c r="B40" s="12" t="inlineStr">
         <is>
           <t>Candle Light Cream</t>
         </is>
       </c>
-      <c r="C40" s="10" t="inlineStr">
+      <c r="C40" s="12" t="inlineStr">
         <is>
           <t>favini.com/gs/en/products/majestic/</t>
         </is>
       </c>
-      <c r="D40" s="10" t="inlineStr">
-        <is>
-          <t>No exact match (Favini: "Candlelight Cream", one word)</t>
-        </is>
-      </c>
-      <c r="E40" s="10" t="inlineStr">
-        <is>
-          <t>No image at all</t>
+      <c r="D40" s="13" t="inlineStr">
+        <is>
+          <t>Mapped (confirmed same product)</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>Real photo applied (Favini: Candlelight Cream)</t>
         </is>
       </c>
     </row>
@@ -1692,81 +1723,270 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
+      <c r="A42" s="12" t="inlineStr">
         <is>
           <t>Majestic</t>
         </is>
       </c>
-      <c r="B42" s="10" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>Real Gold</t>
         </is>
       </c>
-      <c r="C42" s="10" t="inlineStr">
+      <c r="C42" s="12" t="inlineStr">
         <is>
           <t>favini.com/gs/en/products/majestic/</t>
         </is>
       </c>
-      <c r="D42" s="10" t="inlineStr">
-        <is>
-          <t>No exact match (Favini: "Luxus Real Gold")</t>
-        </is>
-      </c>
-      <c r="E42" s="10" t="inlineStr">
-        <is>
-          <t>No image at all</t>
+      <c r="D42" s="13" t="inlineStr">
+        <is>
+          <t>Mapped (confirmed same product)</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>Real photo applied (Favini: Luxus Real Gold)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="inlineStr">
+      <c r="A43" s="15" t="inlineStr">
         <is>
           <t>Classy Covers</t>
         </is>
       </c>
-      <c r="B43" s="10" t="inlineStr">
-        <is>
-          <t>Bianco / Grey / Green / Brown / Coffee / Navy / Cobalt / Nero (all 8)</t>
-        </is>
-      </c>
-      <c r="C43" s="10" t="inlineStr">
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>Grey</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="inlineStr">
         <is>
           <t>favini.com/gs/en/products/classy-covers/</t>
         </is>
       </c>
-      <c r="D43" s="10" t="inlineStr">
-        <is>
-          <t>No exact match — Favini's names all carry finish-code suffixes (Grey TT, White MN, etc.) and use English White/Black not Bianco/Nero</t>
-        </is>
-      </c>
-      <c r="E43" s="10" t="inlineStr">
-        <is>
-          <t>No image at all</t>
+      <c r="D43" s="16" t="inlineStr">
+        <is>
+          <t>Matched, suffix ignored (Favini: Grey TT)</t>
+        </is>
+      </c>
+      <c r="E43" s="16" t="inlineStr">
+        <is>
+          <t>Real photo applied</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>Classy Covers</t>
+        </is>
+      </c>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="inlineStr">
+        <is>
+          <t>favini.com/gs/en/products/classy-covers/</t>
+        </is>
+      </c>
+      <c r="D44" s="16" t="inlineStr">
+        <is>
+          <t>Matched, suffix ignored (Favini: Green TT)</t>
+        </is>
+      </c>
+      <c r="E44" s="16" t="inlineStr">
+        <is>
+          <t>Real photo applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>Classy Covers</t>
+        </is>
+      </c>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>Brown</t>
+        </is>
+      </c>
+      <c r="C45" s="15" t="inlineStr">
+        <is>
+          <t>favini.com/gs/en/products/classy-covers/</t>
+        </is>
+      </c>
+      <c r="D45" s="16" t="inlineStr">
+        <is>
+          <t>Matched, suffix ignored (Favini: Brown TT)</t>
+        </is>
+      </c>
+      <c r="E45" s="16" t="inlineStr">
+        <is>
+          <t>Real photo applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="15" t="inlineStr">
+        <is>
+          <t>Classy Covers</t>
+        </is>
+      </c>
+      <c r="B46" s="15" t="inlineStr">
+        <is>
+          <t>Coffee</t>
+        </is>
+      </c>
+      <c r="C46" s="15" t="inlineStr">
+        <is>
+          <t>favini.com/gs/en/products/classy-covers/</t>
+        </is>
+      </c>
+      <c r="D46" s="16" t="inlineStr">
+        <is>
+          <t>Matched, suffix ignored (Favini: Coffee TT)</t>
+        </is>
+      </c>
+      <c r="E46" s="16" t="inlineStr">
+        <is>
+          <t>Real photo applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="15" t="inlineStr">
+        <is>
+          <t>Classy Covers</t>
+        </is>
+      </c>
+      <c r="B47" s="15" t="inlineStr">
+        <is>
+          <t>Navy</t>
+        </is>
+      </c>
+      <c r="C47" s="15" t="inlineStr">
+        <is>
+          <t>favini.com/gs/en/products/classy-covers/</t>
+        </is>
+      </c>
+      <c r="D47" s="16" t="inlineStr">
+        <is>
+          <t>Matched, suffix ignored (Favini: Navy TT)</t>
+        </is>
+      </c>
+      <c r="E47" s="16" t="inlineStr">
+        <is>
+          <t>Real photo applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>Classy Covers</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>Cobalt</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
+          <t>favini.com/gs/en/products/classy-covers/</t>
+        </is>
+      </c>
+      <c r="D48" s="16" t="inlineStr">
+        <is>
+          <t>Matched, suffix ignored (Favini: Cobalt TT)</t>
+        </is>
+      </c>
+      <c r="E48" s="16" t="inlineStr">
+        <is>
+          <t>Real photo applied</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="17" t="inlineStr">
+        <is>
+          <t>Classy Covers</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="inlineStr">
+        <is>
+          <t>Bianco</t>
+        </is>
+      </c>
+      <c r="C49" s="17" t="inlineStr">
+        <is>
+          <t>favini.com/gs/en/products/classy-covers/</t>
+        </is>
+      </c>
+      <c r="D49" s="18" t="inlineStr">
+        <is>
+          <t>No match — Favini uses English "White", not a suffix issue</t>
+        </is>
+      </c>
+      <c r="E49" s="18" t="inlineStr">
+        <is>
+          <t>No image — placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="17" t="inlineStr">
+        <is>
+          <t>Classy Covers</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="inlineStr">
+        <is>
+          <t>Nero</t>
+        </is>
+      </c>
+      <c r="C50" s="17" t="inlineStr">
+        <is>
+          <t>favini.com/gs/en/products/classy-covers/</t>
+        </is>
+      </c>
+      <c r="D50" s="18" t="inlineStr">
+        <is>
+          <t>No match — Favini uses English "Black", not a suffix issue</t>
+        </is>
+      </c>
+      <c r="E50" s="18" t="inlineStr">
+        <is>
+          <t>No image — placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>In Metal</t>
         </is>
       </c>
-      <c r="B44" s="10" t="inlineStr">
+      <c r="B51" s="10" t="inlineStr">
         <is>
           <t>Ice Gold / White Gold (both)</t>
         </is>
       </c>
-      <c r="C44" s="10" t="inlineStr">
+      <c r="C51" s="10" t="inlineStr">
         <is>
           <t>favini.com/gs/en/products/in-metal/</t>
         </is>
       </c>
-      <c r="D44" s="10" t="inlineStr">
+      <c r="D51" s="10" t="inlineStr">
         <is>
           <t>No exact match (page only shows "White TT"/"White MN"). Also missing isFavini/brand flag in our own data entirely</t>
         </is>
       </c>
-      <c r="E44" s="10" t="inlineStr">
+      <c r="E51" s="10" t="inlineStr">
         <is>
           <t>No image at all</t>
         </is>
